--- a/Project_ETF/ETF_Investment_Portfolio/00981A/ETF_Investment_Portfolio_20260820.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00981A/ETF_Investment_Portfolio_20260820.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D74"/>
+  <dimension ref="A1:D75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>9.96%</t>
+          <t>10.08%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>9.76%</t>
+          <t>9.82%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>8.02%</t>
+          <t>8.05%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>5,348,000</t>
+          <t>5,148,000</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>7.19%</t>
+          <t>6.62%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>6.38%</t>
+          <t>6.12%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>5.11%</t>
+          <t>4.96%</t>
         </is>
       </c>
     </row>
@@ -748,24 +748,24 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>4.96%</t>
+          <t>4.90%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>6,564,000</t>
+          <t>2,486,000</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -777,44 +777,44 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>2,395,000</t>
+          <t>6,564,000</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>4.57%</t>
+          <t>4.81%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>2,442,000</t>
+          <t>2,395,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>4.49%</t>
+          <t>4.66%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>4.34%</t>
+          <t>4.27%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>3.97%</t>
+          <t>4.00%</t>
         </is>
       </c>
     </row>
@@ -897,12 +897,12 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>4,615,848</t>
+          <t>4,671,848</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>3.55%</t>
+          <t>3.66%</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>3.53%</t>
+          <t>3.52%</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.88%</t>
+          <t>3.01%</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.27%</t>
+          <t>2.25%</t>
         </is>
       </c>
     </row>
@@ -980,7 +980,7 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>台指期貨(B)</t>
+          <t>台指期貨</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -990,7 +990,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2.11%</t>
+          <t>2.12%</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.42%</t>
+          <t>1.46%</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>0.92%</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>0.85%</t>
+          <t>0.83%</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>0.73%</t>
+          <t>0.71%</t>
         </is>
       </c>
     </row>
@@ -1100,51 +1100,51 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>0.48%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>1,101,000</t>
+          <t>477,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>0.46%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>477,000</t>
+          <t>1,101,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>0.43%</t>
         </is>
       </c>
     </row>
@@ -1173,22 +1173,22 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>833,000</t>
+          <t>142,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.38%</t>
+          <t>0.28%</t>
         </is>
       </c>
     </row>
@@ -1239,83 +1239,83 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>台表科</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>3,249,000</t>
+          <t>483,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.20%</t>
+          <t>0.21%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>6271</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>同欣電</t>
+          <t>台表科</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>2,223,000</t>
+          <t>3,249,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.15%</t>
+          <t>0.20%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>6191</t>
+          <t>6271</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>精成科</t>
+          <t>同欣電</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>3,988,000</t>
+          <t>2,223,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.12%</t>
+          <t>0.15%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>3376</t>
+          <t>6191</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>新日興</t>
+          <t>精成科</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>1,741,000</t>
+          <t>3,988,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1327,39 +1327,39 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>3376</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>新日興</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>140,000</t>
+          <t>1,741,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.03%</t>
+          <t>0.11%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>5,163,000</t>
+          <t>140,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -1371,56 +1371,56 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>2637</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>慧洋-KY</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>200,000</t>
+          <t>5,163,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.01%</t>
+          <t>0.03%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2637</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>慧洋-KY</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>200,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0.01%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -1437,12 +1437,12 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -1459,12 +1459,12 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>世界</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -1481,12 +1481,12 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>亞德客-KY</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -1503,12 +1503,12 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>世界</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -1525,12 +1525,12 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -1547,12 +1547,12 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -1569,17 +1569,17 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2481</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>強茂</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>5,000</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -1591,12 +1591,12 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>2439</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>美律</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -1613,17 +1613,17 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>強茂</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>5,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -1635,12 +1635,12 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>2439</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>美律</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -1657,12 +1657,12 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -1679,12 +1679,12 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -1701,12 +1701,12 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>亞德客-KY</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
@@ -1733,7 +1733,7 @@
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>7,036,035,601</t>
+          <t>7,047,956,124</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr"/>
@@ -1751,7 +1751,7 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>1,674,969,738</t>
+          <t>1,729,697,138</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr"/>
@@ -1769,10 +1769,28 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>7,017,750,689</t>
+          <t>4,786,505,994</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>RP_NTD</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>RP</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>3,266,182,664</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="5">
